--- a/artfynd/A 25591-2026 artfynd.xlsx
+++ b/artfynd/A 25591-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134232391</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>134232390</v>
       </c>
       <c r="B3" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25591-2026 artfynd.xlsx
+++ b/artfynd/A 25591-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>134232391</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -778,108 +778,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>134232390</v>
-      </c>
-      <c r="B3" t="n">
-        <v>91987</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Umgransele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>661792</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7173380</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25591-2026 artfynd.xlsx
+++ b/artfynd/A 25591-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,8 +783,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232391</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>